--- a/Data/Resultados_Barras/Resultados_Barras_Congruencia.xlsx
+++ b/Data/Resultados_Barras/Resultados_Barras_Congruencia.xlsx
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7968413496051687</v>
+        <v>0.1138344785150241</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.717516152189519</v>
+        <v>-0.1025023074556456</v>
       </c>
       <c r="E2" t="n">
-        <v>3.110308076721872e-41</v>
+        <v>1.07958233755713e-41</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-20.18418395549174</v>
+        <v>-2.883454850784535</v>
       </c>
       <c r="D3" t="n">
-        <v>-18.7597916367552</v>
+        <v>-2.679970233822172</v>
       </c>
       <c r="E3" t="n">
-        <v>2.095496253681971e-18</v>
+        <v>2.093746458967153e-18</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,17 +524,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3373205741626794</v>
+        <v>0.04818865345181135</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2240829346092504</v>
+        <v>-0.03201184780132148</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009005260591428492</v>
+        <v>0.01183013773671107</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -550,13 +550,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-18.37136483253589</v>
+        <v>-2.624480690362269</v>
       </c>
       <c r="D5" t="n">
-        <v>-16.82836403508772</v>
+        <v>-2.404052005012531</v>
       </c>
       <c r="E5" t="n">
-        <v>5.818370526825435e-06</v>
+        <v>5.820519570617477e-06</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
